--- a/EndResult/1500m Fri.xlsx
+++ b/EndResult/1500m Fri.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17.13,75</t>
+          <t>17.13,81</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -655,7 +655,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>08.06.2024</t>
+          <t>19.01.2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1339,12 +1339,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Malin Schanke Tømmervik</t>
+          <t>Ylva S. Dyngeland</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18.39,59</t>
+          <t>18.39,57</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>05.06.2010</t>
+          <t>17.01.2015</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1374,12 +1374,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ylva S. Dyngeland</t>
+          <t>Malin Schanke Tømmervik</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.39,57</t>
+          <t>18.39,59</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>17.01.2015</t>
+          <t>05.06.2010</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">

--- a/EndResult/1500m Fri.xlsx
+++ b/EndResult/1500m Fri.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17.13,81</t>
+          <t>17.13,75</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -655,7 +655,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>08.06.2024</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1339,12 +1339,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ylva S. Dyngeland</t>
+          <t>Malin Schanke Tømmervik</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18.39,57</t>
+          <t>18.39,59</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>17.01.2015</t>
+          <t>05.06.2010</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1374,12 +1374,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Malin Schanke Tømmervik</t>
+          <t>Ylva S. Dyngeland</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.39,59</t>
+          <t>18.39,57</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>05.06.2010</t>
+          <t>17.01.2015</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1880,25 +1880,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Hedda Østgaard</t>
+          <t>Marie Skuseth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21.14,00</t>
+          <t>20.40,85</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>408</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>24.04.2009</t>
+          <t>06.06.2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1915,25 +1915,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Camilla Dahle-Øfsti</t>
+          <t>Hedda Østgaard</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21.23,99</t>
+          <t>21.14,00</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>19.04.2015</t>
+          <t>24.04.2009</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1950,16 +1950,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Edle Lund</t>
+          <t>Camilla Dahle-Øfsti</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22.13,46</t>
+          <t>21.23,99</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>328</v>
+        <v>368</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1985,25 +1985,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Othelie Annette Høie</t>
+          <t>Edle Lund</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>22.27,17</t>
+          <t>22.13,46</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>29.08.2015</t>
+          <t>19.04.2015</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
